--- a/artfynd/S 1326-2024 artfynd.xlsx
+++ b/artfynd/S 1326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129513</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92131743</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92131798</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92180469</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92131659</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129276</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129219</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129812</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129475</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129546</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92131853</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2230,6 +2305,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92129425</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2331,8 +2411,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92131867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>